--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487589_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487589_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0748</v>
+        <v>5.8086</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6164</v>
+        <v>5.4593</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4584</v>
+        <v>0.3493</v>
       </c>
       <c r="G2" t="n">
         <v>3.8881</v>
@@ -610,13 +610,13 @@
         <v>1.7463</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8252</v>
+        <v>-0.0914</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9085</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0833</v>
+        <v>-0.0258</v>
       </c>
       <c r="V2" t="n">
         <v>2.4</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9666</v>
+        <v>4.7113</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7156</v>
+        <v>3.2967</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2511</v>
+        <v>1.4146</v>
       </c>
       <c r="G3" t="n">
         <v>3.5234</v>
@@ -688,13 +688,13 @@
         <v>1.5523</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0074</v>
+        <v>0.752</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4262</v>
+        <v>0.0073</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5812</v>
+        <v>0.7447</v>
       </c>
       <c r="V3" t="n">
         <v>0.0478</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1703</v>
+        <v>4.3764</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1082</v>
+        <v>3.851</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0621</v>
+        <v>0.5254</v>
       </c>
       <c r="G4" t="n">
         <v>2.3483</v>
@@ -766,13 +766,13 @@
         <v>1.9403</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2064</v>
+        <v>-0.0003</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9085</v>
+        <v>-0.1657</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2979</v>
+        <v>0.1655</v>
       </c>
       <c r="V4" t="n">
         <v>0.2821</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7276</v>
+        <v>0.648</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6083</v>
+        <v>0.8285</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1193</v>
+        <v>-0.1805</v>
       </c>
       <c r="G5" t="n">
         <v>0.4831</v>
@@ -844,13 +844,13 @@
         <v>2.3284</v>
       </c>
       <c r="S5" t="n">
-        <v>2.0803</v>
+        <v>1.0007</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9724</v>
+        <v>0.1926</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1079</v>
+        <v>0.8081</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2239</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. GUEYE</t>
+          <t>A. JIMÉNEZ BARRETO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.0112</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3287</v>
+        <v>1.4697</v>
       </c>
       <c r="F6" t="n">
-        <v>1.234</v>
+        <v>-1.4809</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.1712</v>
+        <v>-0.3884</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1236</v>
+        <v>-1.6296</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.0476</v>
+        <v>1.2413</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2439</v>
+        <v>1.5107</v>
       </c>
       <c r="K6" t="n">
-        <v>0.964</v>
+        <v>0.2472</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2078</v>
+        <v>1.2635</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.9273</v>
+        <v>-1.8991</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0875</v>
+        <v>-1.8768</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8398</v>
+        <v>-0.0223</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1642</v>
+        <v>1.7463</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.1045</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9403</v>
+        <v>1.7463</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3571</v>
+        <v>-0.1452</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1839</v>
+        <v>-0.041</v>
       </c>
       <c r="U6" t="n">
-        <v>1.1732</v>
+        <v>-0.1043</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8836</v>
+        <v>-1.2239</v>
       </c>
       <c r="W6" t="n">
-        <v>1.8358</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0478</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="7">
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2918</v>
+        <v>-0.5105</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5529</v>
+        <v>1.3342</v>
       </c>
       <c r="F7" t="n">
         <v>-1.8447</v>
@@ -1000,10 +1000,10 @@
         <v>1.3582</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2187</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3656</v>
+        <v>0.1469</v>
       </c>
       <c r="U7" t="n">
         <v>-0.1469</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. JIMÉNEZ BARRETO</t>
+          <t>S. GUEYE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6051</v>
+        <v>-0.6373</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1484</v>
+        <v>-1.3262</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7535</v>
+        <v>0.6889</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3884</v>
+        <v>-2.1712</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6296</v>
+        <v>-0.1236</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2413</v>
+        <v>-2.0476</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5107</v>
+        <v>-0.2439</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2472</v>
+        <v>0.964</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2635</v>
+        <v>-1.2078</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8991</v>
+        <v>-1.9273</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.8768</v>
+        <v>-1.0875</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0223</v>
+        <v>-0.8398</v>
       </c>
       <c r="P8" t="n">
-        <v>1.7463</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-3.1045</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7463</v>
+        <v>1.9403</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7391</v>
+        <v>0.8146</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3623</v>
+        <v>0.1864</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3768</v>
+        <v>0.6281</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2239</v>
+        <v>1.8836</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.8358</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2239</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9904</v>
+        <v>-1.4204</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8391</v>
+        <v>-0.3781</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1513</v>
+        <v>-1.0423</v>
       </c>
       <c r="G9" t="n">
         <v>0.3401</v>
@@ -1156,13 +1156,13 @@
         <v>1.3582</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2425</v>
+        <v>0.3275</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9085</v>
+        <v>-0.4475</v>
       </c>
       <c r="U9" t="n">
-        <v>0.666</v>
+        <v>0.775</v>
       </c>
       <c r="V9" t="n">
         <v>-1.506</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9794</v>
+        <v>-3.4729</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7242</v>
+        <v>-3.1632</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2552</v>
+        <v>-0.3097</v>
       </c>
       <c r="G10" t="n">
         <v>-4.8849</v>
@@ -1234,13 +1234,13 @@
         <v>1.5523</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.1119</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9691</v>
+        <v>-0.408</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3506</v>
+        <v>0.2961</v>
       </c>
       <c r="V10" t="n">
         <v>0.9418</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>7.9779</v>
+        <v>9.492000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>9.857799999999999</v>
+        <v>11.3719</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8798</v>
+        <v>-1.8799</v>
       </c>
       <c r="G11" t="n">
         <v>2.481700000000001</v>
@@ -1282,7 +1282,7 @@
         <v>2.537599999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.05549999999999988</v>
+        <v>-0.0555000000000001</v>
       </c>
       <c r="J11" t="n">
         <v>17.9907</v>
@@ -1312,13 +1312,13 @@
         <v>15.5226</v>
       </c>
       <c r="S11" t="n">
-        <v>1.0319</v>
+        <v>2.546</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.1088</v>
+        <v>-0.5946</v>
       </c>
       <c r="U11" t="n">
-        <v>3.1406</v>
+        <v>3.1405</v>
       </c>
       <c r="V11" t="n">
         <v>1.5537</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. ALARCON ORTIZ</t>
+          <t>J. AYALA AYLLÓN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4453</v>
+        <v>2.347</v>
       </c>
       <c r="E12" t="n">
-        <v>1.2915</v>
+        <v>4.4027</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1538</v>
+        <v>-2.0557</v>
       </c>
       <c r="G12" t="n">
-        <v>1.1551</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3981</v>
+        <v>-1.3718</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.243</v>
+        <v>2.0588</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7944</v>
+        <v>4.4015</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7538</v>
+        <v>1.1081</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0406</v>
+        <v>3.2934</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3606</v>
+        <v>-3.7145</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6443</v>
+        <v>-2.4799</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2836</v>
+        <v>-1.2346</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3881</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5821</v>
+        <v>1.9403</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4545</v>
+        <v>-0.4579</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2434</v>
+        <v>-0.7406</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2111</v>
+        <v>0.2827</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2239</v>
+        <v>2.1179</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2239</v>
+        <v>2.6821</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. AYALA AYLLÓN</t>
+          <t>M. ALARCON ORTIZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.8098</v>
+        <v>2.0722</v>
       </c>
       <c r="E13" t="n">
-        <v>3.702</v>
+        <v>0.8911</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8921</v>
+        <v>1.1811</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6870000000000001</v>
+        <v>1.1551</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.3718</v>
+        <v>1.3981</v>
       </c>
       <c r="I13" t="n">
-        <v>2.0588</v>
+        <v>-0.243</v>
       </c>
       <c r="J13" t="n">
-        <v>4.4015</v>
+        <v>0.7944</v>
       </c>
       <c r="K13" t="n">
-        <v>1.1081</v>
+        <v>0.7538</v>
       </c>
       <c r="L13" t="n">
-        <v>3.2934</v>
+        <v>0.0406</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.7145</v>
+        <v>0.3606</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.4799</v>
+        <v>0.6443</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.2346</v>
+        <v>-0.2836</v>
       </c>
       <c r="P13" t="n">
+        <v>-0.3881</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.9702</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.5821</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.0813</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.157</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.2384</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.2239</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.2239</v>
+      </c>
+      <c r="X13" t="n">
         <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-1.9403</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.9403</v>
-      </c>
-      <c r="S13" t="n">
-        <v>-0.995</v>
-      </c>
-      <c r="T13" t="n">
-        <v>-1.4413</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0.4462</v>
-      </c>
-      <c r="V13" t="n">
-        <v>2.1179</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.6821</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-0.5642</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.467</v>
+        <v>1.7851</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3971</v>
+        <v>0.4972</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0699</v>
+        <v>1.2879</v>
       </c>
       <c r="G14" t="n">
         <v>1.4243</v>
@@ -1546,13 +1546,13 @@
         <v>1.1642</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.1915</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4722</v>
+        <v>-0.3721</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0374</v>
+        <v>0.1806</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6119</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. SAEZ BENITO</t>
+          <t>M. SANZ CÁMARA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1158</v>
+        <v>0.4819</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9275</v>
+        <v>1.327</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8117</v>
+        <v>-0.8451</v>
       </c>
       <c r="G15" t="n">
-        <v>0.09760000000000001</v>
+        <v>-1.1118</v>
       </c>
       <c r="H15" t="n">
-        <v>0.463</v>
+        <v>0.1005</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3654</v>
+        <v>-1.2123</v>
       </c>
       <c r="J15" t="n">
-        <v>0.988</v>
+        <v>1.1992</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9475</v>
+        <v>1.7219</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0406</v>
+        <v>-0.5227000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8904</v>
+        <v>-2.311</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4844</v>
+        <v>-1.6214</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.406</v>
+        <v>-0.6896</v>
       </c>
       <c r="P15" t="n">
         <v>0.194</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R15" t="n">
-        <v>0.194</v>
+        <v>1.1642</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1759</v>
+        <v>0.1758</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0606</v>
+        <v>-0.408</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1153</v>
+        <v>0.5838</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. SANZ CÁMARA</t>
+          <t>J. SAEZ BENITO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0086</v>
+        <v>0.1431</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8265</v>
+        <v>0.9275</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8178</v>
+        <v>-0.7844</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.1118</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1005</v>
+        <v>0.463</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.2123</v>
+        <v>-0.3654</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1992</v>
+        <v>0.988</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7219</v>
+        <v>0.9475</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5227000000000001</v>
+        <v>0.0406</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.311</v>
+        <v>-0.8904</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.6214</v>
+        <v>-0.4844</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6896</v>
+        <v>-0.406</v>
       </c>
       <c r="P16" t="n">
         <v>0.194</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1642</v>
+        <v>0.194</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2974</v>
+        <v>-0.1486</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9085</v>
+        <v>-0.0606</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6111</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. TRUJILLO FERNÁNDEZ</t>
+          <t>M. BATLLE BERNARDO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5095</v>
+        <v>-0.4759</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0194</v>
+        <v>1.0744</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4901</v>
+        <v>-1.5502</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4416</v>
+        <v>0.4871</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1747</v>
+        <v>1.0043</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2669</v>
+        <v>-0.5172</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0412</v>
+        <v>3.2766</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0412</v>
+        <v>2.6982</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.5784</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4004</v>
+        <v>-2.7895</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1335</v>
+        <v>-1.6939</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2669</v>
+        <v>-1.0956</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3881</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3881</v>
+        <v>1.3582</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1153</v>
+        <v>-0.051</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0606</v>
+        <v>-0.544</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0547</v>
+        <v>0.493</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2239</v>
+        <v>-0.3299</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2239</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. BATLLE BERNARDO</t>
+          <t>J. TRUJILLO FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7212</v>
+        <v>-0.4823</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0744</v>
+        <v>-0.0194</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7955</v>
+        <v>-0.4629</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4871</v>
+        <v>0.4416</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0043</v>
+        <v>0.1747</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5172</v>
+        <v>0.2669</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2766</v>
+        <v>0.0412</v>
       </c>
       <c r="K18" t="n">
-        <v>2.6982</v>
+        <v>0.0412</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5784</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.7895</v>
+        <v>0.4004</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.6939</v>
+        <v>0.1335</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0956</v>
+        <v>0.2669</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.5821</v>
+        <v>0.3881</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3582</v>
+        <v>0.3881</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2963</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.544</v>
+        <v>-0.0606</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2477</v>
+        <v>-0.0275</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3299</v>
+        <v>-1.2239</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6119</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ GREGORIO</t>
+          <t>M. DEL VALLE REGALADO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.924</v>
+        <v>-1.8803</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7644</v>
+        <v>-1.6655</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6884</v>
+        <v>-0.2148</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1497</v>
+        <v>0.3096</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5835</v>
+        <v>-0.6303</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4338</v>
+        <v>0.9398</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5506</v>
+        <v>1.8198</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9722</v>
+        <v>0.4573</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5784</v>
+        <v>1.3625</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7003</v>
+        <v>-1.5102</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.5557</v>
+        <v>-1.0875</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1446</v>
+        <v>-0.4227</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9702</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9403</v>
+        <v>-2.9105</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9702</v>
+        <v>1.7463</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1958</v>
+        <v>-0.4615</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1541</v>
+        <v>-0.5748</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0417</v>
+        <v>0.1133</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.5642</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. DEL VALLE REGALADO</t>
+          <t>S. RODRIGUEZ GREGORIO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.917</v>
+        <v>-1.9979</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8657</v>
+        <v>-0.3367</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0512</v>
+        <v>-1.6611</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3096</v>
+        <v>-1.1497</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6303</v>
+        <v>-1.5835</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9398</v>
+        <v>0.4338</v>
       </c>
       <c r="J20" t="n">
-        <v>1.8198</v>
+        <v>1.5506</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4573</v>
+        <v>0.9722</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3625</v>
+        <v>0.5784</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5102</v>
+        <v>-2.7003</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0875</v>
+        <v>-2.5557</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4227</v>
+        <v>-0.1446</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1642</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9105</v>
+        <v>-1.9403</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7463</v>
+        <v>0.9702</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4982</v>
+        <v>0.122</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.775</v>
+        <v>0.053</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2768</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5642</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3308</v>
+        <v>-3.3947</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4447</v>
+        <v>-0.6449</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.886</v>
+        <v>-2.7497</v>
       </c>
       <c r="G21" t="n">
         <v>-2.6105</v>
@@ -2092,13 +2092,13 @@
         <v>1.7463</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2725</v>
+        <v>-0.3365</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.35</v>
+        <v>-0.5502</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0774</v>
+        <v>0.2137</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2239</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.4221</v>
+        <v>-6.5762</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.7736</v>
+        <v>-4.5734</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6485</v>
+        <v>-2.0028</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2122</v>
@@ -2170,13 +2170,13 @@
         <v>1.3582</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4783</v>
+        <v>0.3241</v>
       </c>
       <c r="T22" t="n">
-        <v>0.074</v>
+        <v>0.2742</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4043</v>
+        <v>0.0499</v>
       </c>
       <c r="V22" t="n">
         <v>-2.1657</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.9781</v>
+        <v>-7.978000000000001</v>
       </c>
       <c r="E23" t="n">
         <v>1.88</v>
       </c>
       <c r="F23" t="n">
-        <v>-9.8576</v>
+        <v>-9.857699999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-2.4819</v>
@@ -2218,16 +2218,16 @@
         <v>-2.537599999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.05560000000000009</v>
+        <v>0.05560000000000032</v>
       </c>
       <c r="J23" t="n">
         <v>15.5088</v>
       </c>
       <c r="K23" t="n">
-        <v>9.919499999999999</v>
+        <v>9.919500000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>5.589300000000001</v>
+        <v>5.5893</v>
       </c>
       <c r="M23" t="n">
         <v>-17.9907</v>
@@ -2236,7 +2236,7 @@
         <v>-12.457</v>
       </c>
       <c r="O23" t="n">
-        <v>-5.533600000000001</v>
+        <v>-5.533599999999999</v>
       </c>
       <c r="P23" t="n">
         <v>-2.9106</v>
@@ -2248,7 +2248,7 @@
         <v>12.6121</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0316</v>
+        <v>-1.0318</v>
       </c>
       <c r="T23" t="n">
         <v>-3.1407</v>
@@ -2260,7 +2260,7 @@
         <v>-1.5538</v>
       </c>
       <c r="W23" t="n">
-        <v>5.034400000000001</v>
+        <v>5.0344</v>
       </c>
       <c r="X23" t="n">
         <v>-6.588100000000001</v>
